--- a/workbooks/06 Formulas 3 - Conditional Math.xlsx
+++ b/workbooks/06 Formulas 3 - Conditional Math.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="634">
   <si>
     <t>Challenge</t>
   </si>
@@ -2024,6 +2024,30 @@
   </si>
   <si>
     <t>Boss F8</t>
+  </si>
+  <si>
+    <t>The date keys plus Shift.</t>
+  </si>
+  <si>
+    <t>CTRL+:</t>
+  </si>
+  <si>
+    <t>CTRL+SHIFT+:</t>
+  </si>
+  <si>
+    <t>CTRL+SHIFT+;</t>
+  </si>
+  <si>
+    <t>CTRL+SHIFT+COLON</t>
+  </si>
+  <si>
+    <t>SHIFT+CTRL+:</t>
+  </si>
+  <si>
+    <t>SHIFT+CTRL+;</t>
+  </si>
+  <si>
+    <t>SHIFT+CTRL+COLON</t>
   </si>
   <si>
     <t>F8</t>
@@ -3007,7 +3031,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3017,12 +3041,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3032,32 +3056,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3067,30 +3091,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F3-1 Counters'!$G$13:$G$39)&amp;" / 200"</f>
@@ -3105,15 +3129,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F3-2 Money Bags'!$G$12:$G$35)&amp;" / 170"</f>
@@ -3128,15 +3152,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F3-3 Multi-Filter'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3151,15 +3175,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM('F3-4 Extremes'!$G$14:$G$42)&amp;" / 220"</f>
@@ -3174,15 +3198,15 @@
         <v>NEW</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="C17" s="9" cm="1" t="str">
         <f t="array" ref="C17">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3197,12 +3221,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="7" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="B19" s="12" cm="1" t="str">
         <f t="array" ref="B19">(SUM('F3-1 Counters'!$G$13:$G$39)+SUM('F3-2 Money Bags'!$G$12:$G$35)+SUM('F3-3 Multi-Filter'!$G$13:$G$38)+SUM('F3-4 Extremes'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))&amp;" / 940"</f>
@@ -3211,19 +3235,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">_xlfn.LET(_xlpm.p,(SUM('F3-1 Counters'!$G$13:$G$39)+SUM('F3-2 Money Bags'!$G$12:$G$35)+SUM('F3-3 Multi-Filter'!$G$13:$G$38)+SUM('F3-4 Extremes'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))/940,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=15),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 15)","—")</f>
@@ -3232,7 +3256,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="B22" s="12" cm="1" t="str">
         <f t="array" ref="B22">IFERROR(INDEX($A$13:$A$16,MATCH("☆☆☆",$D$13:$D$16,0))&amp;" "&amp;INDEX($B$13:$B$16,MATCH("☆☆☆",$D$13:$D$16,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
@@ -3241,7 +3265,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="13" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
     </row>
   </sheetData>
@@ -3278,7 +3302,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3289,7 +3313,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -3556,15 +3580,15 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B21" s="32" cm="1" t="str">
-        <f t="array" ref="B21">IF($C$10="OPEN","Which function adds values that meet one condition?  (from F3-2 Money Bags)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
+        <f t="array" ref="B21">IF($C$10="OPEN","Which keys type the current time as a fixed value?  (from S2-3 Stamps &amp; Smart Fill)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
-        <f t="array" ref="D21">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$21,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$87:$J$87),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
+        <f t="array" ref="D21">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$21,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$87:$K$87),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E21" s="22"/>
@@ -3579,7 +3603,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -3590,7 +3614,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3618,14 +3642,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B26" s="32" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In M6 count the North orders.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$6),ABS('Boss Arena'!$M$6-Key!$C$88)&lt;=1E-9*MAX(1,ABS(Key!$C$88))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTIF"))))),"LOCKED")</f>
@@ -3643,14 +3667,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="B27" s="32" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In M7 add the Revenue of all Gadget orders.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$7),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$7),ABS('Boss Arena'!$M$7-Key!$C$89)&lt;=1E-9*MAX(1,ABS(Key!$C$89))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUMIF"))))),"LOCKED")</f>
@@ -3668,14 +3692,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="B28" s="32" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In M8 average Lee's Units.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$8),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$8),ABS('Boss Arena'!$M$8-Key!$C$90)&lt;=1E-9*MAX(1,ABS(Key!$C$90))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGEIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use AVERAGEIF"))))),"LOCKED")</f>
@@ -3693,14 +3717,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="B29" s="32" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In M9 count South orders with more than 20 units.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$9),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$9),ABS('Boss Arena'!$M$9-Key!$C$91)&lt;=1E-9*MAX(1,ABS(Key!$C$91))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTIFS"))))),"LOCKED")</f>
@@ -3718,14 +3742,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="B30" s="32" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In M10 add the Revenue of Raj's Gizmo orders.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$10),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$10)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$10),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$10),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$10),ABS('Boss Arena'!$M$10-Key!$C$92)&lt;=1E-9*MAX(1,ABS(Key!$C$92))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$10)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUMIFS"))))),"LOCKED")</f>
@@ -3743,14 +3767,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="B31" s="32" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In M11 find the smallest Units among East orders.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$11),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$11)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$11),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$11),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$11),ABS('Boss Arena'!$M$11-Key!$C$93)&lt;=1E-9*MAX(1,ABS(Key!$C$93))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MINIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$11)))))),"✔ CLEAR","✘ CLOSE · right value, but use MINIFS"))))),"LOCKED")</f>
@@ -3768,14 +3792,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="B32" s="32" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In M12 count orders with Units ≥ K6, building the criteria with ""&gt;=""&amp;K6.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$12),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$12)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$12),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$12),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$12),ABS('Boss Arena'!$M$12-Key!$C$94)&lt;=1E-9*MAX(1,ABS(Key!$C$94))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$12)))))),IF(ISNUMBER(FIND("&amp;",_xlfn.FORMULATEXT('Boss Arena'!$M$12))),"✔ CLEAR","✘ CLOSE · your formula needs &amp;"),"✘ CLOSE · right value, but use COUNTIFS"))))),"LOCKED")</f>
@@ -3793,14 +3817,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="B33" s="32" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","In M13 add the Revenue dated from K9 to K11.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$13),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$13)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$13),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$13),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$13),ABS('Boss Arena'!$M$13-Key!$C$95)&lt;=1E-9*MAX(1,ABS(Key!$C$95))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$13)))))),IF(ISNUMBER(FIND("&amp;",_xlfn.FORMULATEXT('Boss Arena'!$M$13))),"✔ CLEAR","✘ CLOSE · your formula needs &amp;"),"✘ CLOSE · right value, but use SUMIFS"))))),"LOCKED")</f>
@@ -4497,7 +4521,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4505,189 +4529,189 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>57</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.75" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>60</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>66</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="35.5" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>145</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="35.5" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>205</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>146</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="35.5" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>285</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="35.5" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>287</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="35.5" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>147</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>248</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>153</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>152</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
     </row>
   </sheetData>
@@ -6166,7 +6190,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:11">
       <c r="A81" t="s">
         <v>516</v>
       </c>
@@ -6192,7 +6216,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:11">
       <c r="A82" t="s">
         <v>518</v>
       </c>
@@ -6206,7 +6230,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:11">
       <c r="A83" t="s">
         <v>520</v>
       </c>
@@ -6220,7 +6244,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:11">
       <c r="A84" t="s">
         <v>521</v>
       </c>
@@ -6246,7 +6270,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:11">
       <c r="A85" t="s">
         <v>523</v>
       </c>
@@ -6257,7 +6281,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:11">
       <c r="A86" t="s">
         <v>525</v>
       </c>
@@ -6271,59 +6295,62 @@
         <v>173</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:11">
       <c r="A87" t="s">
         <v>527</v>
       </c>
       <c r="B87" t="s">
-        <v>244</v>
+        <v>528</v>
       </c>
       <c r="E87" t="s">
-        <v>252</v>
+        <v>529</v>
       </c>
       <c r="F87" t="s">
-        <v>253</v>
+        <v>530</v>
       </c>
       <c r="G87" t="s">
-        <v>254</v>
+        <v>531</v>
       </c>
       <c r="H87" t="s">
-        <v>145</v>
+        <v>532</v>
       </c>
       <c r="I87" t="s">
-        <v>255</v>
+        <v>533</v>
       </c>
       <c r="J87" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
+        <v>534</v>
+      </c>
+      <c r="K87" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="B88" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C88" cm="1">
         <f t="array" ref="C88">COUNTIF('Boss Arena'!$D$6:$D$25,"North")</f>
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="B89" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="C89" cm="1">
         <f t="array" ref="C89">SUMIF('Boss Arena'!$F$6:$F$25,"Gadget",'Boss Arena'!$H$6:$H$25)</f>
         <v>15900</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="B90" t="s">
         <v>268</v>
@@ -6333,33 +6360,33 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="B91" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="C91" cm="1">
         <f t="array" ref="C91">COUNTIFS('Boss Arena'!$D$6:$D$25,"South",'Boss Arena'!$G$6:$G$25,"&gt;20")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="B92" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="C92" cm="1">
         <f t="array" ref="C92">SUMIFS('Boss Arena'!$H$6:$H$25,'Boss Arena'!$E$6:$E$25,"Raj",'Boss Arena'!$F$6:$F$25,"Gizmo")</f>
         <v>5500</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="B93" t="s">
         <v>484</v>
@@ -6369,9 +6396,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="B94" t="s">
         <v>488</v>
@@ -6381,12 +6408,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="B95" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="C95" cm="1">
         <f t="array" ref="C95">SUMIFS('Boss Arena'!$H$6:$H$25,'Boss Arena'!$C$6:$C$25,"&gt;="&amp;'Boss Arena'!$K$9,'Boss Arena'!$C$6:$C$25,"&lt;="&amp;'Boss Arena'!$K$11)</f>

--- a/workbooks/06 Formulas 3 - Conditional Math.xlsx
+++ b/workbooks/06 Formulas 3 - Conditional Math.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="638">
   <si>
     <t>Challenge</t>
   </si>
@@ -619,64 +619,70 @@
     <t>T2</t>
   </si>
   <si>
+    <t>Pick the COUNTIF criteria for "greater than 50", quotes included.</t>
+  </si>
+  <si>
+    <t>F3-1 Counters T3</t>
+  </si>
+  <si>
+    <t>Shift+8.</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>Which move is this? * matches any text, ? one character: "G*" = starts with G.</t>
+  </si>
+  <si>
+    <t>CHALLENGES · recall it, then do it</t>
+  </si>
+  <si>
+    <t>▶ Open F3-1 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F3-1 Counters C1</t>
+  </si>
+  <si>
+    <t>=COUNTIF</t>
+  </si>
+  <si>
+    <t>=COUNTIF(</t>
+  </si>
+  <si>
+    <t>=COUNTIF()</t>
+  </si>
+  <si>
+    <t>COUNTIF(</t>
+  </si>
+  <si>
+    <t>COUNTIF()</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>F3-1 Counters C2</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
     <t>Type the COUNTIF criteria for "greater than 50", quotes included.</t>
   </si>
   <si>
-    <t>F3-1 Counters T3</t>
-  </si>
-  <si>
-    <t>Shift+8.</t>
-  </si>
-  <si>
-    <t>T3</t>
+    <t>F3-1 Counters C3</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>ASTERISK</t>
+  </si>
+  <si>
+    <t>C3</t>
   </si>
   <si>
     <t>Which wildcard matches any number of characters?</t>
-  </si>
-  <si>
-    <t>CHALLENGES · recall it, then do it</t>
-  </si>
-  <si>
-    <t>▶ Open F3-1 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F3-1 Counters C1</t>
-  </si>
-  <si>
-    <t>=COUNTIF</t>
-  </si>
-  <si>
-    <t>=COUNTIF(</t>
-  </si>
-  <si>
-    <t>=COUNTIF()</t>
-  </si>
-  <si>
-    <t>COUNTIF(</t>
-  </si>
-  <si>
-    <t>COUNTIF()</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>F3-1 Counters C2</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>F3-1 Counters C3</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>ASTERISK</t>
-  </si>
-  <si>
-    <t>C3</t>
   </si>
   <si>
     <t>F3-1 Counters C4</t>
@@ -1810,73 +1816,79 @@
     <t>Shift+7.</t>
   </si>
   <si>
+    <t>Which move is this? Join an operator to a cell with &amp;: "&gt;="&amp;K6.</t>
+  </si>
+  <si>
+    <t>F3-4 Extremes T4</t>
+  </si>
+  <si>
+    <t>One pair per edge.</t>
+  </si>
+  <si>
+    <t>T4</t>
+  </si>
+  <si>
+    <t>Which move is this? Dates between two days: one criteria pair for &gt;= start, one for &lt;= end.</t>
+  </si>
+  <si>
+    <t>▶ Open F3-4 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F3-4 Extremes C1</t>
+  </si>
+  <si>
+    <t>=MAXIFS</t>
+  </si>
+  <si>
+    <t>=MAXIFS(</t>
+  </si>
+  <si>
+    <t>=MAXIFS()</t>
+  </si>
+  <si>
+    <t>MAXIFS(</t>
+  </si>
+  <si>
+    <t>MAXIFS()</t>
+  </si>
+  <si>
+    <t>F3-4 Extremes C2</t>
+  </si>
+  <si>
+    <t>=MINIFS</t>
+  </si>
+  <si>
+    <t>=MINIFS(</t>
+  </si>
+  <si>
+    <t>=MINIFS()</t>
+  </si>
+  <si>
+    <t>MINIFS(</t>
+  </si>
+  <si>
+    <t>MINIFS()</t>
+  </si>
+  <si>
+    <t>F3-4 Extremes C3</t>
+  </si>
+  <si>
+    <t>&amp;</t>
+  </si>
+  <si>
+    <t>AMPERSAND</t>
+  </si>
+  <si>
     <t>Which character joins "&gt;=" to a cell reference in criteria?</t>
   </si>
   <si>
-    <t>F3-4 Extremes T4</t>
-  </si>
-  <si>
-    <t>One pair per edge.</t>
-  </si>
-  <si>
-    <t>T4</t>
+    <t>F3-4 Extremes C4</t>
+  </si>
+  <si>
+    <t>TWO</t>
   </si>
   <si>
     <t>How many range/criteria pairs do you need for 'dates between a start and an end'?</t>
-  </si>
-  <si>
-    <t>▶ Open F3-4 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F3-4 Extremes C1</t>
-  </si>
-  <si>
-    <t>=MAXIFS</t>
-  </si>
-  <si>
-    <t>=MAXIFS(</t>
-  </si>
-  <si>
-    <t>=MAXIFS()</t>
-  </si>
-  <si>
-    <t>MAXIFS(</t>
-  </si>
-  <si>
-    <t>MAXIFS()</t>
-  </si>
-  <si>
-    <t>F3-4 Extremes C2</t>
-  </si>
-  <si>
-    <t>=MINIFS</t>
-  </si>
-  <si>
-    <t>=MINIFS(</t>
-  </si>
-  <si>
-    <t>=MINIFS()</t>
-  </si>
-  <si>
-    <t>MINIFS(</t>
-  </si>
-  <si>
-    <t>MINIFS()</t>
-  </si>
-  <si>
-    <t>F3-4 Extremes C3</t>
-  </si>
-  <si>
-    <t>&amp;</t>
-  </si>
-  <si>
-    <t>AMPERSAND</t>
-  </si>
-  <si>
-    <t>F3-4 Extremes C4</t>
-  </si>
-  <si>
-    <t>TWO</t>
   </si>
   <si>
     <t>F3-4 Extremes C5</t>
@@ -3031,7 +3043,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3041,12 +3053,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3056,32 +3068,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3091,30 +3103,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F3-1 Counters'!$G$13:$G$39)&amp;" / 200"</f>
@@ -3129,15 +3141,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F3-2 Money Bags'!$G$12:$G$35)&amp;" / 170"</f>
@@ -3152,15 +3164,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F3-3 Multi-Filter'!$G$13:$G$38)&amp;" / 190"</f>
@@ -3175,15 +3187,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM('F3-4 Extremes'!$G$14:$G$42)&amp;" / 220"</f>
@@ -3198,15 +3210,15 @@
         <v>NEW</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C17" s="9" cm="1" t="str">
         <f t="array" ref="C17">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3221,12 +3233,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="7" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B19" s="12" cm="1" t="str">
         <f t="array" ref="B19">(SUM('F3-1 Counters'!$G$13:$G$39)+SUM('F3-2 Money Bags'!$G$12:$G$35)+SUM('F3-3 Multi-Filter'!$G$13:$G$38)+SUM('F3-4 Extremes'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))&amp;" / 940"</f>
@@ -3235,19 +3247,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">_xlfn.LET(_xlpm.p,(SUM('F3-1 Counters'!$G$13:$G$39)+SUM('F3-2 Money Bags'!$G$12:$G$35)+SUM('F3-3 Multi-Filter'!$G$13:$G$38)+SUM('F3-4 Extremes'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))/940,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=15),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 15)","—")</f>
@@ -3256,7 +3268,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B22" s="12" cm="1" t="str">
         <f t="array" ref="B22">IFERROR(INDEX($A$13:$A$16,MATCH("☆☆☆",$D$13:$D$16,0))&amp;" "&amp;INDEX($B$13:$B$16,MATCH("☆☆☆",$D$13:$D$16,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
@@ -3265,7 +3277,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="13" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -3302,7 +3314,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3313,7 +3325,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -3332,7 +3344,7 @@
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -3343,19 +3355,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="7" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C6" s="30"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="7" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C7" s="30"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="7" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C8" s="31" cm="1" t="str">
         <f t="array" ref="C8">IF(OR(C6="",C7=""),"",ROUND(MOD(C7-C6,1)*1440,0))</f>
@@ -3364,7 +3376,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="7" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C9" s="31">
         <v>15</v>
@@ -3372,7 +3384,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="7" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C10" s="12" cm="1" t="str">
         <f t="array" ref="C10">IF(AND(SUM('F3-1 Counters'!$G$13:$G$39)&gt;=200*0.5,SUM('F3-2 Money Bags'!$G$12:$G$35)&gt;=170*0.5,SUM('F3-3 Multi-Filter'!$G$13:$G$38)&gt;=190*0.5,SUM('F3-4 Extremes'!$G$14:$G$42)&gt;=220*0.5),"OPEN","LOCKED")</f>
@@ -3385,7 +3397,7 @@
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -3419,7 +3431,7 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B14" s="32" cm="1" t="str">
         <f t="array" ref="B14">IF($C$10="OPEN","Which function returns the largest value that meets conditions?  (from F3-4 Extremes)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3442,7 +3454,7 @@
     </row>
     <row r="15" spans="1:7" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B15" s="32" cm="1" t="str">
         <f t="array" ref="B15">IF($C$10="OPEN","Which function returns the smallest value that meets conditions?  (from F3-4 Extremes)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3465,7 +3477,7 @@
     </row>
     <row r="16" spans="1:7" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B16" s="32" cm="1" t="str">
         <f t="array" ref="B16">IF($C$10="OPEN","Which character joins ""&gt;="" to a cell reference in criteria?  (from F3-4 Extremes)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3488,7 +3500,7 @@
     </row>
     <row r="17" spans="1:7" ht="51.25" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B17" s="32" cm="1" t="str">
         <f t="array" ref="B17">IF($C$10="OPEN","How many range/criteria pairs do you need for 'dates between a start and an end'?  (from F3-4 Extremes)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3511,7 +3523,7 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B18" s="32" cm="1" t="str">
         <f t="array" ref="B18">IF($C$10="OPEN","Which function counts cells that meet one condition?  (from F3-1 Counters)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3534,7 +3546,7 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B19" s="32" cm="1" t="str">
         <f t="array" ref="B19">IF($C$10="OPEN","Type the COUNTIF criteria for ""greater than 50"", quotes included.  (from F3-1 Counters)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3557,7 +3569,7 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B20" s="32" cm="1" t="str">
         <f t="array" ref="B20">IF($C$10="OPEN","Which wildcard matches any number of characters?  (from F3-1 Counters)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3580,7 +3592,7 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B21" s="32" cm="1" t="str">
         <f t="array" ref="B21">IF($C$10="OPEN","Which keys type the current time as a fixed value?  (from S2-3 Stamps &amp; Smart Fill)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -3603,7 +3615,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -3614,7 +3626,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3642,14 +3654,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B26" s="32" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In M6 count the North orders.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$6),ABS('Boss Arena'!$M$6-Key!$C$88)&lt;=1E-9*MAX(1,ABS(Key!$C$88))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTIF"))))),"LOCKED")</f>
@@ -3667,14 +3679,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B27" s="32" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In M7 add the Revenue of all Gadget orders.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$7),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$7),ABS('Boss Arena'!$M$7-Key!$C$89)&lt;=1E-9*MAX(1,ABS(Key!$C$89))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUMIF"))))),"LOCKED")</f>
@@ -3692,14 +3704,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B28" s="32" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In M8 average Lee's Units.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$8),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$8),ABS('Boss Arena'!$M$8-Key!$C$90)&lt;=1E-9*MAX(1,ABS(Key!$C$90))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGEIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use AVERAGEIF"))))),"LOCKED")</f>
@@ -3717,14 +3729,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B29" s="32" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In M9 count South orders with more than 20 units.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$9),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$9),ABS('Boss Arena'!$M$9-Key!$C$91)&lt;=1E-9*MAX(1,ABS(Key!$C$91))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTIFS"))))),"LOCKED")</f>
@@ -3742,14 +3754,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B30" s="32" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In M10 add the Revenue of Raj's Gizmo orders.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$10),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$10)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$10),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$10),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$10),ABS('Boss Arena'!$M$10-Key!$C$92)&lt;=1E-9*MAX(1,ABS(Key!$C$92))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$10)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUMIFS"))))),"LOCKED")</f>
@@ -3767,14 +3779,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B31" s="32" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In M11 find the smallest Units among East orders.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$11),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$11)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$11),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$11),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$11),ABS('Boss Arena'!$M$11-Key!$C$93)&lt;=1E-9*MAX(1,ABS(Key!$C$93))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MINIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$11)))))),"✔ CLEAR","✘ CLOSE · right value, but use MINIFS"))))),"LOCKED")</f>
@@ -3792,14 +3804,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B32" s="32" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In M12 count orders with Units ≥ K6, building the criteria with ""&gt;=""&amp;K6.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$12),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$12)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$12),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$12),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$12),ABS('Boss Arena'!$M$12-Key!$C$94)&lt;=1E-9*MAX(1,ABS(Key!$C$94))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$12)))))),IF(ISNUMBER(FIND("&amp;",_xlfn.FORMULATEXT('Boss Arena'!$M$12))),"✔ CLEAR","✘ CLOSE · your formula needs &amp;"),"✘ CLOSE · right value, but use COUNTIFS"))))),"LOCKED")</f>
@@ -3817,14 +3829,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B33" s="32" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","In M13 add the Revenue dated from K9 to K11.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$13),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$13)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$13),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$13),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$13),ABS('Boss Arena'!$M$13-Key!$C$95)&lt;=1E-9*MAX(1,ABS(Key!$C$95))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$13)))))),IF(ISNUMBER(FIND("&amp;",_xlfn.FORMULATEXT('Boss Arena'!$M$13))),"✔ CLEAR","✘ CLOSE · your formula needs &amp;"),"✘ CLOSE · right value, but use SUMIFS"))))),"LOCKED")</f>
@@ -3944,7 +3956,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -3957,10 +3969,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4015,7 +4027,7 @@
         <v>40</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="M6" s="29"/>
     </row>
@@ -4042,7 +4054,7 @@
         <v>900</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="M7" s="29"/>
     </row>
@@ -4072,7 +4084,7 @@
         <v>48</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="M8" s="29"/>
     </row>
@@ -4102,7 +4114,7 @@
         <v>46054</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="M9" s="29"/>
     </row>
@@ -4132,7 +4144,7 @@
         <v>49</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="M10" s="29"/>
     </row>
@@ -4162,7 +4174,7 @@
         <v>46112</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="M11" s="29"/>
     </row>
@@ -4189,7 +4201,7 @@
         <v>1500</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M12" s="29"/>
     </row>
@@ -4216,7 +4228,7 @@
         <v>2250</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M13" s="29"/>
     </row>
@@ -4521,7 +4533,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4529,189 +4541,189 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>57</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.75" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>60</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>66</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="35.5" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>145</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="35.5" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>146</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="35.5" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="35.5" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="35.5" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>147</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>153</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>152</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
   </sheetData>
@@ -5015,24 +5027,24 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B17" t="s">
         <v>157</v>
       </c>
       <c r="E17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B18" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C18" cm="1">
         <f t="array" ref="C18">COUNTIF('F3-1 Arena'!$D$6:$D$25,"East")</f>
@@ -5041,10 +5053,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C19" cm="1">
         <f t="array" ref="C19">COUNTIF('F3-1 Arena'!$G$6:$G$25,"&gt;50")</f>
@@ -5053,10 +5065,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B20" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C20" cm="1">
         <f t="array" ref="C20">COUNTIF('F3-1 Arena'!$F$6:$F$25,"G*")</f>
@@ -5065,10 +5077,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B21" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C21" cm="1">
         <f t="array" ref="C21">COUNTIF('F3-1 Arena'!$D$6:$D$25,"&lt;&gt;East")</f>
@@ -5077,7 +5089,7 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B22" t="s">
         <v>144</v>
@@ -5103,7 +5115,7 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B23" t="s">
         <v>151</v>
@@ -5114,110 +5126,110 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B24" t="s">
         <v>157</v>
       </c>
       <c r="E24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B25" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E25" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F25" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B26" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E26" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F26" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B27" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E27" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F27" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B28" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E28" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B29" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E29" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B30" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E30" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B31" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B32" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C32" t="s">
         <v>145</v>
@@ -5232,27 +5244,27 @@
         <v>145</v>
       </c>
       <c r="H32" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="33" spans="1:20">
       <c r="A33" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B33" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C33" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E33" t="s">
         <v>145</v>
       </c>
       <c r="F33" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G33" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H33" t="s">
         <v>60</v>
@@ -5260,62 +5272,62 @@
     </row>
     <row r="34" spans="1:20">
       <c r="A34" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B34" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E34" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F34" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G34" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H34" t="s">
         <v>145</v>
       </c>
       <c r="I34" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J34" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35" spans="1:20">
       <c r="A35" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B35" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E35" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F35" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G35" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H35" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I35" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J35" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36" spans="1:20">
       <c r="A36" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B36" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C36" cm="1">
         <f t="array" ref="C36">SUMIF('F3-2 Arena'!$D$6:$D$25,"West",'F3-2 Arena'!$H$6:$H$25)</f>
@@ -5324,10 +5336,10 @@
     </row>
     <row r="37" spans="1:20">
       <c r="A37" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B37" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C37" cm="1">
         <f t="array" ref="C37">AVERAGEIF('F3-2 Arena'!$E$6:$E$25,"Kim",'F3-2 Arena'!$G$6:$G$25)</f>
@@ -5336,10 +5348,10 @@
     </row>
     <row r="38" spans="1:20">
       <c r="A38" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B38" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C38" cm="1">
         <f t="array" ref="C38">SUMIF('F3-2 Arena'!$G$6:$G$25,"&gt;=40",'F3-2 Arena'!$H$6:$H$25)</f>
@@ -5348,319 +5360,319 @@
     </row>
     <row r="39" spans="1:20">
       <c r="A39" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B39" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E39" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F39" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G39" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H39" t="s">
         <v>145</v>
       </c>
       <c r="I39" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J39" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:20">
       <c r="A40" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B40" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E40" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G40" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H40" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I40" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J40" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="41" spans="1:20">
       <c r="A41" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B41" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E41" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="42" spans="1:20">
       <c r="A42" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B42" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E42" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F42" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G42" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H42" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:20">
       <c r="A43" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B43" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G43" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H43" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:20">
       <c r="A44" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E44" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F44" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="45" spans="1:20">
       <c r="A45" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E45" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F45" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G45" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H45" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I45" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J45" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K45" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L45" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M45" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N45" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O45" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P45" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q45" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="R45" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="S45" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="T45" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="46" spans="1:20">
       <c r="A46" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B46" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E46" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F46" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G46" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H46" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I46" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J46" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K46" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L46" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M46" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N46" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O46" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="P46" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q46" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="R46" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="S46" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="T46" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="47" spans="1:20">
       <c r="A47" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B47" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E47" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F47" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="48" spans="1:20">
       <c r="A48" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B48" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E48" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B49" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C49" t="s">
         <v>146</v>
       </c>
       <c r="E49" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F49" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G49" t="s">
         <v>146</v>
       </c>
       <c r="H49" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B50" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E50" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F50" t="s">
         <v>145</v>
       </c>
       <c r="G50" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H50" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B51" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C51" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E51" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F51" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G51" t="s">
         <v>147</v>
@@ -5671,88 +5683,88 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B52" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E52" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F52" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G52" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H52" t="s">
         <v>146</v>
       </c>
       <c r="I52" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J52" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B53" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E53" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F53" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G53" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H53" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I53" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J53" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B54" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E54" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F54" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G54" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H54" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I54" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J54" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C55" cm="1">
         <f t="array" ref="C55">COUNTIFS('F3-3 Arena'!$D$6:$D$25,"East",'F3-3 Arena'!$G$6:$G$25,"&gt;30")</f>
@@ -5761,10 +5773,10 @@
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B56" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C56" cm="1">
         <f t="array" ref="C56">SUMIFS('F3-3 Arena'!$H$6:$H$25,'F3-3 Arena'!$D$6:$D$25,"East",'F3-3 Arena'!$F$6:$F$25,"Widget")</f>
@@ -5773,10 +5785,10 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B57" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C57" cm="1">
         <f t="array" ref="C57">AVERAGEIFS('F3-3 Arena'!$H$6:$H$25,'F3-3 Arena'!$E$6:$E$25,"Kim",'F3-3 Arena'!$D$6:$D$25,"East")</f>
@@ -5785,183 +5797,183 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B58" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E58" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F58" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G58" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H58" t="s">
         <v>146</v>
       </c>
       <c r="I58" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J58" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B59" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E59" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F59" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G59" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H59" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I59" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J59" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B60" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E60" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F60" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G60" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H60" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I60" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J60" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B61" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E61" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B62" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E62" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B63" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E63" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F63" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B64" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E64" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B65" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E65" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B66" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E66" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B67" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E67" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F67" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B68" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C68" t="s">
         <v>147</v>
       </c>
       <c r="E68" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F68" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G68" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H68" t="s">
         <v>147</v>
@@ -5969,19 +5981,19 @@
     </row>
     <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B69" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C69" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E69" t="s">
         <v>147</v>
       </c>
       <c r="F69" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G69" t="s">
         <v>145</v>
@@ -5992,10 +6004,10 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B70" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C70" t="s">
         <v>153</v>
@@ -6015,10 +6027,10 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B71" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C71" t="s">
         <v>152</v>
@@ -6038,90 +6050,90 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B72" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E72" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F72" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G72" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="H72" t="s">
         <v>147</v>
       </c>
       <c r="I72" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J72" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B73" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E73" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F73" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="G73" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="H73" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I73" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J73" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B74" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E74" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F74" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B75" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E75" t="s">
         <v>61</v>
       </c>
       <c r="F75" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B76" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C76" cm="1">
         <f t="array" ref="C76">_xlfn.MAXIFS('F3-4 Arena'!$H$6:$H$25,'F3-4 Arena'!$D$6:$D$25,"East")</f>
@@ -6130,10 +6142,10 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B77" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C77" cm="1">
         <f t="array" ref="C77">_xlfn.MINIFS('F3-4 Arena'!$G$6:$G$25,'F3-4 Arena'!$F$6:$F$25,"Widget")</f>
@@ -6142,10 +6154,10 @@
     </row>
     <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B78" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C78" cm="1">
         <f t="array" ref="C78">COUNTIF('F3-4 Arena'!$G$6:$G$25,"&gt;="&amp;'F3-4 Arena'!$K$6)</f>
@@ -6154,10 +6166,10 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B79" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C79" cm="1">
         <f t="array" ref="C79">SUMIFS('F3-4 Arena'!$H$6:$H$25,'F3-4 Arena'!$C$6:$C$25,"&gt;="&amp;'F3-4 Arena'!$K$9,'F3-4 Arena'!$C$6:$C$25,"&lt;="&amp;'F3-4 Arena'!$K$11)</f>
@@ -6166,87 +6178,87 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B80" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E80" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F80" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G80" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="H80" t="s">
         <v>147</v>
       </c>
       <c r="I80" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J80" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B81" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E81" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F81" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="G81" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="H81" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I81" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J81" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B82" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E82" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F82" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B83" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E83" t="s">
         <v>61</v>
       </c>
       <c r="F83" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B84" t="s">
         <v>144</v>
@@ -6272,7 +6284,7 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B85" t="s">
         <v>151</v>
@@ -6283,53 +6295,53 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B86" t="s">
         <v>157</v>
       </c>
       <c r="E86" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F86" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B87" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E87" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="F87" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="G87" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="H87" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="I87" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="J87" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="K87" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B88" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C88" cm="1">
         <f t="array" ref="C88">COUNTIF('Boss Arena'!$D$6:$D$25,"North")</f>
@@ -6338,10 +6350,10 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B89" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C89" cm="1">
         <f t="array" ref="C89">SUMIF('Boss Arena'!$F$6:$F$25,"Gadget",'Boss Arena'!$H$6:$H$25)</f>
@@ -6350,10 +6362,10 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B90" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C90" cm="1">
         <f t="array" ref="C90">AVERAGEIF('Boss Arena'!$E$6:$E$25,"Lee",'Boss Arena'!$G$6:$G$25)</f>
@@ -6362,10 +6374,10 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B91" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C91" cm="1">
         <f t="array" ref="C91">COUNTIFS('Boss Arena'!$D$6:$D$25,"South",'Boss Arena'!$G$6:$G$25,"&gt;20")</f>
@@ -6374,10 +6386,10 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B92" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="C92" cm="1">
         <f t="array" ref="C92">SUMIFS('Boss Arena'!$H$6:$H$25,'Boss Arena'!$E$6:$E$25,"Raj",'Boss Arena'!$F$6:$F$25,"Gizmo")</f>
@@ -6386,10 +6398,10 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B93" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C93" cm="1">
         <f t="array" ref="C93">_xlfn.MINIFS('Boss Arena'!$G$6:$G$25,'Boss Arena'!$D$6:$D$25,"East")</f>
@@ -6398,10 +6410,10 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B94" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C94" cm="1">
         <f t="array" ref="C94">COUNTIFS('Boss Arena'!$G$6:$G$25,"&gt;="&amp;'Boss Arena'!$K$6)</f>
@@ -6410,10 +6422,10 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B95" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C95" cm="1">
         <f t="array" ref="C95">SUMIFS('Boss Arena'!$H$6:$H$25,'Boss Arena'!$C$6:$C$25,"&gt;="&amp;'Boss Arena'!$K$9,'Boss Arena'!$C$6:$C$25,"&lt;="&amp;'Boss Arena'!$K$11)</f>
@@ -6445,7 +6457,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6456,7 +6468,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -6956,7 +6968,7 @@
         <v>170</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -6975,10 +6987,10 @@
     </row>
     <row r="35" spans="1:7" ht="35.5" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -6997,13 +7009,13 @@
     </row>
     <row r="36" spans="1:7" ht="35.5" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F3-1 Arena'!$M$6),"",IF(NOT(_xlfn.ISFORMULA('F3-1 Arena'!$M$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-1 Arena'!$M$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-1 Arena'!$M$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-1 Arena'!$M$6),ABS('F3-1 Arena'!$M$6-Key!$C$18)&lt;=1E-9*MAX(1,ABS(Key!$C$18))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-1 Arena'!$M$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTIF")))))</f>
@@ -7021,13 +7033,13 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(ISBLANK('F3-1 Arena'!$M$7),"",IF(NOT(_xlfn.ISFORMULA('F3-1 Arena'!$M$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-1 Arena'!$M$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-1 Arena'!$M$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-1 Arena'!$M$7),ABS('F3-1 Arena'!$M$7-Key!$C$19)&lt;=1E-9*MAX(1,ABS(Key!$C$19))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-1 Arena'!$M$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTIF")))))</f>
@@ -7045,13 +7057,13 @@
     </row>
     <row r="38" spans="1:7" ht="35.5" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F3-1 Arena'!$M$8),"",IF(NOT(_xlfn.ISFORMULA('F3-1 Arena'!$M$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-1 Arena'!$M$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-1 Arena'!$M$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-1 Arena'!$M$8),ABS('F3-1 Arena'!$M$8-Key!$C$20)&lt;=1E-9*MAX(1,ABS(Key!$C$20))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-1 Arena'!$M$8)))))),IF(ISNUMBER(FIND("*",_xlfn.FORMULATEXT('F3-1 Arena'!$M$8))),"✔ CLEAR","✘ CLOSE · your formula needs *"),"✘ CLOSE · right value, but use COUNTIF")))))</f>
@@ -7069,13 +7081,13 @@
     </row>
     <row r="39" spans="1:7" ht="19.75" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(ISBLANK('F3-1 Arena'!$M$9),"",IF(NOT(_xlfn.ISFORMULA('F3-1 Arena'!$M$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-1 Arena'!$M$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-1 Arena'!$M$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-1 Arena'!$M$9),ABS('F3-1 Arena'!$M$9-Key!$C$21)&lt;=1E-9*MAX(1,ABS(Key!$C$21))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-1 Arena'!$M$9)))))),IF(ISNUMBER(FIND("&lt;&gt;",_xlfn.FORMULATEXT('F3-1 Arena'!$M$9))),"✔ CLEAR","✘ CLOSE · your formula needs &lt;&gt;"),"✘ CLOSE · right value, but use COUNTIF")))))</f>
@@ -7779,7 +7791,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7790,7 +7802,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -7842,7 +7854,7 @@
         <v>58</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>145</v>
@@ -7853,10 +7865,10 @@
         <v>61</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="22" customHeight="1">
@@ -7898,7 +7910,7 @@
         <v>79</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="21" cm="1" t="str">
@@ -7920,7 +7932,7 @@
         <v>87</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -7942,7 +7954,7 @@
         <v>95</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -7964,7 +7976,7 @@
         <v>103</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -7986,7 +7998,7 @@
         <v>111</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -8008,7 +8020,7 @@
         <v>119</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -8030,7 +8042,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -8052,7 +8064,7 @@
         <v>130</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -8074,7 +8086,7 @@
         <v>135</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -8096,7 +8108,7 @@
         <v>140</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -8152,7 +8164,7 @@
         <v>148</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="21" cm="1" t="str">
@@ -8174,7 +8186,7 @@
         <v>154</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -8204,7 +8216,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="B29" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -8235,7 +8247,7 @@
         <v>168</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" cm="1" t="str">
@@ -8257,7 +8269,7 @@
         <v>170</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21" cm="1" t="str">
@@ -8276,13 +8288,13 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF(ISBLANK('F3-2 Arena'!$M$6),"",IF(NOT(_xlfn.ISFORMULA('F3-2 Arena'!$M$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-2 Arena'!$M$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-2 Arena'!$M$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-2 Arena'!$M$6),ABS('F3-2 Arena'!$M$6-Key!$C$36)&lt;=1E-9*MAX(1,ABS(Key!$C$36))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-2 Arena'!$M$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUMIF")))))</f>
@@ -8300,13 +8312,13 @@
     </row>
     <row r="34" spans="1:7" ht="35.5" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D34" s="21" cm="1" t="str">
         <f t="array" ref="D34">IF(ISBLANK('F3-2 Arena'!$M$7),"",IF(NOT(_xlfn.ISFORMULA('F3-2 Arena'!$M$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-2 Arena'!$M$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-2 Arena'!$M$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-2 Arena'!$M$7),ABS('F3-2 Arena'!$M$7-Key!$C$37)&lt;=1E-9*MAX(1,ABS(Key!$C$37))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGEIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-2 Arena'!$M$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use AVERAGEIF")))))</f>
@@ -8324,13 +8336,13 @@
     </row>
     <row r="35" spans="1:7" ht="35.5" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D35" s="21" cm="1" t="str">
         <f t="array" ref="D35">IF(ISBLANK('F3-2 Arena'!$M$8),"",IF(NOT(_xlfn.ISFORMULA('F3-2 Arena'!$M$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-2 Arena'!$M$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-2 Arena'!$M$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-2 Arena'!$M$8),ABS('F3-2 Arena'!$M$8-Key!$C$38)&lt;=1E-9*MAX(1,ABS(Key!$C$38))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-2 Arena'!$M$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUMIF")))))</f>
@@ -8456,7 +8468,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -8469,10 +8481,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -8527,7 +8539,7 @@
         <v>40</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M6" s="29"/>
     </row>
@@ -8554,7 +8566,7 @@
         <v>900</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M7" s="29"/>
     </row>
@@ -8584,7 +8596,7 @@
         <v>48</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M8" s="29"/>
     </row>
@@ -9016,7 +9028,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9027,7 +9039,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -9079,7 +9091,7 @@
         <v>58</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>146</v>
@@ -9090,10 +9102,10 @@
         <v>61</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="67" customHeight="1">
@@ -9101,10 +9113,10 @@
         <v>64</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="22" customHeight="1">
@@ -9146,7 +9158,7 @@
         <v>79</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -9168,7 +9180,7 @@
         <v>87</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -9190,7 +9202,7 @@
         <v>95</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -9212,7 +9224,7 @@
         <v>103</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -9234,7 +9246,7 @@
         <v>111</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -9256,7 +9268,7 @@
         <v>119</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -9278,7 +9290,7 @@
         <v>125</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -9300,7 +9312,7 @@
         <v>130</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -9322,7 +9334,7 @@
         <v>135</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -9344,7 +9356,7 @@
         <v>140</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -9400,7 +9412,7 @@
         <v>148</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -9422,7 +9434,7 @@
         <v>154</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -9444,7 +9456,7 @@
         <v>158</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -9474,7 +9486,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="B31" s="11" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -9505,7 +9517,7 @@
         <v>168</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -9527,7 +9539,7 @@
         <v>170</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -9546,10 +9558,10 @@
     </row>
     <row r="35" spans="1:7" ht="35.5" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -9568,13 +9580,13 @@
     </row>
     <row r="36" spans="1:7" ht="35.5" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F3-3 Arena'!$M$6),"",IF(NOT(_xlfn.ISFORMULA('F3-3 Arena'!$M$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-3 Arena'!$M$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-3 Arena'!$M$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-3 Arena'!$M$6),ABS('F3-3 Arena'!$M$6-Key!$C$55)&lt;=1E-9*MAX(1,ABS(Key!$C$55))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-3 Arena'!$M$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTIFS")))))</f>
@@ -9592,13 +9604,13 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
         <f t="array" ref="D37">IF(ISBLANK('F3-3 Arena'!$M$7),"",IF(NOT(_xlfn.ISFORMULA('F3-3 Arena'!$M$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-3 Arena'!$M$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-3 Arena'!$M$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-3 Arena'!$M$7),ABS('F3-3 Arena'!$M$7-Key!$C$56)&lt;=1E-9*MAX(1,ABS(Key!$C$56))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-3 Arena'!$M$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUMIFS")))))</f>
@@ -9616,13 +9628,13 @@
     </row>
     <row r="38" spans="1:7" ht="19.75" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
         <f t="array" ref="D38">IF(ISBLANK('F3-3 Arena'!$M$8),"",IF(NOT(_xlfn.ISFORMULA('F3-3 Arena'!$M$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-3 Arena'!$M$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-3 Arena'!$M$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-3 Arena'!$M$8),ABS('F3-3 Arena'!$M$8-Key!$C$57)&lt;=1E-9*MAX(1,ABS(Key!$C$57))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGEIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-3 Arena'!$M$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use AVERAGEIFS")))))</f>
@@ -9758,7 +9770,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -9771,10 +9783,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -9829,7 +9841,7 @@
         <v>40</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M6" s="29"/>
     </row>
@@ -9856,7 +9868,7 @@
         <v>900</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M7" s="29"/>
     </row>
@@ -9886,7 +9898,7 @@
         <v>48</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M8" s="29"/>
     </row>
@@ -10318,7 +10330,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10329,7 +10341,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -10381,7 +10393,7 @@
         <v>58</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>147</v>
@@ -10392,10 +10404,10 @@
         <v>61</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.5" customHeight="1">
@@ -10403,7 +10415,7 @@
         <v>64</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>153</v>
@@ -10411,10 +10423,10 @@
     </row>
     <row r="10" spans="1:7" ht="67" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>152</v>
@@ -10459,7 +10471,7 @@
         <v>79</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -10481,7 +10493,7 @@
         <v>87</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -10503,7 +10515,7 @@
         <v>95</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -10525,7 +10537,7 @@
         <v>103</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -10547,7 +10559,7 @@
         <v>111</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -10569,7 +10581,7 @@
         <v>119</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -10591,7 +10603,7 @@
         <v>125</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -10613,7 +10625,7 @@
         <v>130</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -10635,7 +10647,7 @@
         <v>135</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -10657,7 +10669,7 @@
         <v>140</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" cm="1" t="str">
@@ -10713,7 +10725,7 @@
         <v>148</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -10735,7 +10747,7 @@
         <v>154</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -10757,7 +10769,7 @@
         <v>158</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="21" cm="1" t="str">
@@ -10776,10 +10788,10 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="21" cm="1" t="str">
@@ -10809,7 +10821,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="11" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -10840,7 +10852,7 @@
         <v>168</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -10862,7 +10874,7 @@
         <v>170</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="21" cm="1" t="str">
@@ -10881,10 +10893,10 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>456</v>
+        <v>479</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="21" cm="1" t="str">
@@ -10903,10 +10915,10 @@
     </row>
     <row r="38" spans="1:7" ht="35.5" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -10925,13 +10937,13 @@
     </row>
     <row r="39" spans="1:7" ht="35.5" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(ISBLANK('F3-4 Arena'!$M$6),"",IF(NOT(_xlfn.ISFORMULA('F3-4 Arena'!$M$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-4 Arena'!$M$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-4 Arena'!$M$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-4 Arena'!$M$6),ABS('F3-4 Arena'!$M$6-Key!$C$76)&lt;=1E-9*MAX(1,ABS(Key!$C$76))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MAXIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-4 Arena'!$M$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use MAXIFS")))))</f>
@@ -10949,13 +10961,13 @@
     </row>
     <row r="40" spans="1:7" ht="35.5" customHeight="1">
       <c r="A40" s="18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D40" s="21" cm="1" t="str">
         <f t="array" ref="D40">IF(ISBLANK('F3-4 Arena'!$M$7),"",IF(NOT(_xlfn.ISFORMULA('F3-4 Arena'!$M$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-4 Arena'!$M$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-4 Arena'!$M$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-4 Arena'!$M$7),ABS('F3-4 Arena'!$M$7-Key!$C$77)&lt;=1E-9*MAX(1,ABS(Key!$C$77))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MINIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-4 Arena'!$M$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use MINIFS")))))</f>
@@ -10973,13 +10985,13 @@
     </row>
     <row r="41" spans="1:7" ht="51.25" customHeight="1">
       <c r="A41" s="18" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="D41" s="21" cm="1" t="str">
         <f t="array" ref="D41">IF(ISBLANK('F3-4 Arena'!$M$8),"",IF(NOT(_xlfn.ISFORMULA('F3-4 Arena'!$M$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-4 Arena'!$M$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-4 Arena'!$M$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-4 Arena'!$M$8),ABS('F3-4 Arena'!$M$8-Key!$C$78)&lt;=1E-9*MAX(1,ABS(Key!$C$78))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-4 Arena'!$M$8)))))),IF(ISNUMBER(FIND("&amp;",_xlfn.FORMULATEXT('F3-4 Arena'!$M$8))),"✔ CLEAR","✘ CLOSE · your formula needs &amp;"),"✘ CLOSE · right value, but use COUNTIF")))))</f>
@@ -10997,13 +11009,13 @@
     </row>
     <row r="42" spans="1:7" ht="51.25" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="D42" s="21" cm="1" t="str">
         <f t="array" ref="D42">IF(ISBLANK('F3-4 Arena'!$M$9),"",IF(NOT(_xlfn.ISFORMULA('F3-4 Arena'!$M$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-4 Arena'!$M$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-4 Arena'!$M$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-4 Arena'!$M$9),ABS('F3-4 Arena'!$M$9-Key!$C$79)&lt;=1E-9*MAX(1,ABS(Key!$C$79))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-4 Arena'!$M$9)))))),IF(ISNUMBER(FIND("&amp;",_xlfn.FORMULATEXT('F3-4 Arena'!$M$9))),"✔ CLEAR","✘ CLOSE · your formula needs &amp;"),"✘ CLOSE · right value, but use SUMIFS")))))</f>
@@ -11153,7 +11165,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -11166,10 +11178,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -11224,7 +11236,7 @@
         <v>40</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M6" s="29"/>
     </row>
@@ -11251,7 +11263,7 @@
         <v>900</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M7" s="29"/>
     </row>
@@ -11281,7 +11293,7 @@
         <v>48</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M8" s="29"/>
     </row>
@@ -11311,7 +11323,7 @@
         <v>46054</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M9" s="29"/>
     </row>

--- a/workbooks/06 Formulas 3 - Conditional Math.xlsx
+++ b/workbooks/06 Formulas 3 - Conditional Math.xlsx
@@ -2269,7 +2269,7 @@
     <t>NEXT UP</t>
   </si>
   <si>
-    <t>Replay a stage: select its yellow answer cells and press Delete. Undo an arena drill with Ctrl+Z.</t>
+    <t>Replay a stage: select a run of its yellow cells (Ctrl+click to add more), then press Delete. Undo an arena drill with Ctrl+Z.</t>
   </si>
   <si>
     <t>CHEAT CODES ▸ CONDITIONAL MATH</t>
@@ -3271,7 +3271,7 @@
         <v>608</v>
       </c>
       <c r="B22" s="12" cm="1" t="str">
-        <f t="array" ref="B22">IFERROR(INDEX($A$13:$A$16,MATCH("☆☆☆",$D$13:$D$16,0))&amp;" "&amp;INDEX($B$13:$B$16,MATCH("☆☆☆",$D$13:$D$16,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
+        <f t="array" ref="B22">IFERROR(INDEX($A$13:$A$16,MATCH("☆☆☆",$D$13:$D$16,0))&amp;" "&amp;INDEX($B$13:$B$16,MATCH("☆☆☆",$D$13:$D$16,0)),IF(Start!$E$17="DEFEATED","All clear! Aim for rank S","the Boss"))</f>
         <v>F3-1 Counters</v>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
         <v>546</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
-        <f t="array" ref="D26">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$6),ABS('Boss Arena'!$M$6-Key!$C$88)&lt;=1E-9*MAX(1,ABS(Key!$C$88))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTIF"))))),"LOCKED")</f>
+        <f t="array" ref="D26">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$6),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$6),ABS('Boss Arena'!$M$6-Key!$C$88)&lt;=1E-9*MAX(1,ABS(Key!$C$88))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$6))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$6))))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTIF/COUNTIFS"))))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E26" s="22"/>
@@ -3689,7 +3689,7 @@
         <v>550</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
-        <f t="array" ref="D27">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$7),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$7),ABS('Boss Arena'!$M$7-Key!$C$89)&lt;=1E-9*MAX(1,ABS(Key!$C$89))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUMIF"))))),"LOCKED")</f>
+        <f t="array" ref="D27">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$7),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$7),ABS('Boss Arena'!$M$7-Key!$C$89)&lt;=1E-9*MAX(1,ABS(Key!$C$89))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$7))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$7))))))),"✔ CLEAR","✘ CLOSE · right value, but use SUMIF/SUMIFS"))))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E27" s="22"/>
@@ -3714,7 +3714,7 @@
         <v>553</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
-        <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$8),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$8),ABS('Boss Arena'!$M$8-Key!$C$90)&lt;=1E-9*MAX(1,ABS(Key!$C$90))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGEIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use AVERAGEIF"))))),"LOCKED")</f>
+        <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$8),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$8),ABS('Boss Arena'!$M$8-Key!$C$90)&lt;=1E-9*MAX(1,ABS(Key!$C$90))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGEIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$8))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGEIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$8))))))),"✔ CLEAR","✘ CLOSE · right value, but use AVERAGEIF/AVERAGEIFS"))))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E28" s="22"/>
@@ -3814,7 +3814,7 @@
         <v>567</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
-        <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$12),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$12)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$12),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$12),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$12),ABS('Boss Arena'!$M$12-Key!$C$94)&lt;=1E-9*MAX(1,ABS(Key!$C$94))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$12)))))),IF(ISNUMBER(FIND("&amp;",_xlfn.FORMULATEXT('Boss Arena'!$M$12))),"✔ CLEAR","✘ CLOSE · your formula needs &amp;"),"✘ CLOSE · right value, but use COUNTIFS"))))),"LOCKED")</f>
+        <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$M$12),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$M$12)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$M$12),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$M$12),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$M$12),ABS('Boss Arena'!$M$12-Key!$C$94)&lt;=1E-9*MAX(1,ABS(Key!$C$94))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$12))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$M$12))))))),IF(ISNUMBER(FIND("&amp;",_xlfn.FORMULATEXT('Boss Arena'!$M$12))),"✔ CLEAR","✘ CLOSE · your formula needs &amp;"),"✘ CLOSE · right value, but use COUNTIF/COUNTIFS"))))),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E32" s="22"/>
@@ -7042,7 +7042,7 @@
         <v>186</v>
       </c>
       <c r="D37" s="21" cm="1" t="str">
-        <f t="array" ref="D37">IF(ISBLANK('F3-1 Arena'!$M$7),"",IF(NOT(_xlfn.ISFORMULA('F3-1 Arena'!$M$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-1 Arena'!$M$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-1 Arena'!$M$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-1 Arena'!$M$7),ABS('F3-1 Arena'!$M$7-Key!$C$19)&lt;=1E-9*MAX(1,ABS(Key!$C$19))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-1 Arena'!$M$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTIF")))))</f>
+        <f t="array" ref="D37">IF(ISBLANK('F3-1 Arena'!$M$7),"",IF(NOT(_xlfn.ISFORMULA('F3-1 Arena'!$M$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-1 Arena'!$M$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-1 Arena'!$M$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-1 Arena'!$M$7),ABS('F3-1 Arena'!$M$7-Key!$C$19)&lt;=1E-9*MAX(1,ABS(Key!$C$19))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-1 Arena'!$M$7))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-1 Arena'!$M$7))))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTIF/COUNTIFS")))))</f>
         <v/>
       </c>
       <c r="E37" s="22"/>
@@ -7066,7 +7066,7 @@
         <v>191</v>
       </c>
       <c r="D38" s="21" cm="1" t="str">
-        <f t="array" ref="D38">IF(ISBLANK('F3-1 Arena'!$M$8),"",IF(NOT(_xlfn.ISFORMULA('F3-1 Arena'!$M$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-1 Arena'!$M$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-1 Arena'!$M$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-1 Arena'!$M$8),ABS('F3-1 Arena'!$M$8-Key!$C$20)&lt;=1E-9*MAX(1,ABS(Key!$C$20))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-1 Arena'!$M$8)))))),IF(ISNUMBER(FIND("*",_xlfn.FORMULATEXT('F3-1 Arena'!$M$8))),"✔ CLEAR","✘ CLOSE · your formula needs *"),"✘ CLOSE · right value, but use COUNTIF")))))</f>
+        <f t="array" ref="D38">IF(ISBLANK('F3-1 Arena'!$M$8),"",IF(NOT(_xlfn.ISFORMULA('F3-1 Arena'!$M$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-1 Arena'!$M$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-1 Arena'!$M$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-1 Arena'!$M$8),ABS('F3-1 Arena'!$M$8-Key!$C$20)&lt;=1E-9*MAX(1,ABS(Key!$C$20))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-1 Arena'!$M$8))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-1 Arena'!$M$8))))))),IF(ISNUMBER(FIND("*",_xlfn.FORMULATEXT('F3-1 Arena'!$M$8))),"✔ CLEAR","✘ CLOSE · your formula needs *"),"✘ CLOSE · right value, but use COUNTIF/COUNTIFS")))))</f>
         <v/>
       </c>
       <c r="E38" s="22"/>
@@ -7090,7 +7090,7 @@
         <v>196</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
-        <f t="array" ref="D39">IF(ISBLANK('F3-1 Arena'!$M$9),"",IF(NOT(_xlfn.ISFORMULA('F3-1 Arena'!$M$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-1 Arena'!$M$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-1 Arena'!$M$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-1 Arena'!$M$9),ABS('F3-1 Arena'!$M$9-Key!$C$21)&lt;=1E-9*MAX(1,ABS(Key!$C$21))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-1 Arena'!$M$9)))))),IF(ISNUMBER(FIND("&lt;&gt;",_xlfn.FORMULATEXT('F3-1 Arena'!$M$9))),"✔ CLEAR","✘ CLOSE · your formula needs &lt;&gt;"),"✘ CLOSE · right value, but use COUNTIF")))))</f>
+        <f t="array" ref="D39">IF(ISBLANK('F3-1 Arena'!$M$9),"",IF(NOT(_xlfn.ISFORMULA('F3-1 Arena'!$M$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-1 Arena'!$M$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-1 Arena'!$M$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-1 Arena'!$M$9),ABS('F3-1 Arena'!$M$9-Key!$C$21)&lt;=1E-9*MAX(1,ABS(Key!$C$21))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-1 Arena'!$M$9))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-1 Arena'!$M$9))))))),IF(ISNUMBER(FIND("&lt;&gt;",_xlfn.FORMULATEXT('F3-1 Arena'!$M$9))),"✔ CLEAR","✘ CLOSE · your formula needs &lt;&gt;"),"✘ CLOSE · right value, but use COUNTIF/COUNTIFS")))))</f>
         <v/>
       </c>
       <c r="E39" s="22"/>
@@ -8321,7 +8321,7 @@
         <v>272</v>
       </c>
       <c r="D34" s="21" cm="1" t="str">
-        <f t="array" ref="D34">IF(ISBLANK('F3-2 Arena'!$M$7),"",IF(NOT(_xlfn.ISFORMULA('F3-2 Arena'!$M$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-2 Arena'!$M$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-2 Arena'!$M$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-2 Arena'!$M$7),ABS('F3-2 Arena'!$M$7-Key!$C$37)&lt;=1E-9*MAX(1,ABS(Key!$C$37))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGEIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-2 Arena'!$M$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use AVERAGEIF")))))</f>
+        <f t="array" ref="D34">IF(ISBLANK('F3-2 Arena'!$M$7),"",IF(NOT(_xlfn.ISFORMULA('F3-2 Arena'!$M$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-2 Arena'!$M$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-2 Arena'!$M$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-2 Arena'!$M$7),ABS('F3-2 Arena'!$M$7-Key!$C$37)&lt;=1E-9*MAX(1,ABS(Key!$C$37))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGEIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-2 Arena'!$M$7))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGEIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-2 Arena'!$M$7))))))),"✔ CLEAR","✘ CLOSE · right value, but use AVERAGEIF/AVERAGEIFS")))))</f>
         <v/>
       </c>
       <c r="E34" s="22"/>
@@ -8345,7 +8345,7 @@
         <v>276</v>
       </c>
       <c r="D35" s="21" cm="1" t="str">
-        <f t="array" ref="D35">IF(ISBLANK('F3-2 Arena'!$M$8),"",IF(NOT(_xlfn.ISFORMULA('F3-2 Arena'!$M$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-2 Arena'!$M$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-2 Arena'!$M$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-2 Arena'!$M$8),ABS('F3-2 Arena'!$M$8-Key!$C$38)&lt;=1E-9*MAX(1,ABS(Key!$C$38))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-2 Arena'!$M$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUMIF")))))</f>
+        <f t="array" ref="D35">IF(ISBLANK('F3-2 Arena'!$M$8),"",IF(NOT(_xlfn.ISFORMULA('F3-2 Arena'!$M$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-2 Arena'!$M$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-2 Arena'!$M$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-2 Arena'!$M$8),ABS('F3-2 Arena'!$M$8-Key!$C$38)&lt;=1E-9*MAX(1,ABS(Key!$C$38))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-2 Arena'!$M$8))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUMIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-2 Arena'!$M$8))))))),"✔ CLEAR","✘ CLOSE · right value, but use SUMIF/SUMIFS")))))</f>
         <v/>
       </c>
       <c r="E35" s="22"/>
@@ -10994,7 +10994,7 @@
         <v>494</v>
       </c>
       <c r="D41" s="21" cm="1" t="str">
-        <f t="array" ref="D41">IF(ISBLANK('F3-4 Arena'!$M$8),"",IF(NOT(_xlfn.ISFORMULA('F3-4 Arena'!$M$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-4 Arena'!$M$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-4 Arena'!$M$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-4 Arena'!$M$8),ABS('F3-4 Arena'!$M$8-Key!$C$78)&lt;=1E-9*MAX(1,ABS(Key!$C$78))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-4 Arena'!$M$8)))))),IF(ISNUMBER(FIND("&amp;",_xlfn.FORMULATEXT('F3-4 Arena'!$M$8))),"✔ CLEAR","✘ CLOSE · your formula needs &amp;"),"✘ CLOSE · right value, but use COUNTIF")))))</f>
+        <f t="array" ref="D41">IF(ISBLANK('F3-4 Arena'!$M$8),"",IF(NOT(_xlfn.ISFORMULA('F3-4 Arena'!$M$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F3-4 Arena'!$M$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F3-4 Arena'!$M$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F3-4 Arena'!$M$8),ABS('F3-4 Arena'!$M$8-Key!$C$78)&lt;=1E-9*MAX(1,ABS(Key!$C$78))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIF"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-4 Arena'!$M$8))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTIFS"&amp;"(",UPPER(_xlfn.FORMULATEXT('F3-4 Arena'!$M$8))))))),IF(ISNUMBER(FIND("&amp;",_xlfn.FORMULATEXT('F3-4 Arena'!$M$8))),"✔ CLEAR","✘ CLOSE · your formula needs &amp;"),"✘ CLOSE · right value, but use COUNTIF/COUNTIFS")))))</f>
         <v/>
       </c>
       <c r="E41" s="22"/>
